--- a/REVIEW/00_Outreach/OUTREACH_LIST.xlsx
+++ b/REVIEW/00_Outreach/OUTREACH_LIST.xlsx
@@ -599,7 +599,7 @@
       <c r="J2" s="4" t="inlineStr"/>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>FPs and checklists print 'Maverick Partner': correct to 'Maverick Parker' (or as he confirms) in every FP before lodging</t>
+          <t>Rev G FPs and checklists print 'Maverick Partner' (TN-1640786 Rev H already says Parker): correct the other bids before lodging</t>
         </is>
       </c>
     </row>
